--- a/output/2025/rosters-end-of-season-2025-ffl.xlsx
+++ b/output/2025/rosters-end-of-season-2025-ffl.xlsx
@@ -233,7 +233,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>South Town FF</t>
+          <t>South Town Freedom Fighters</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
